--- a/src/assets/hq-sales-summary-template.xlsx
+++ b/src/assets/hq-sales-summary-template.xlsx
@@ -14,12 +14,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'monthly sales'!$A4:$N77</definedName>
   </definedNames>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="72">
   <si>
     <t>SEED MALAYSIA JAN - JAN ~DEC 2026 SALES REPORT</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Wohlk KE RGP</t>
+  </si>
+  <si>
+    <t>Wohlk Contact Life Sph</t>
+  </si>
+  <si>
+    <t>Wohlk Contact Life Toric</t>
   </si>
   <si>
     <t>DISOP H2O2 SOLUTION</t>
@@ -354,7 +360,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="84">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -682,27 +688,6 @@
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -873,6 +858,13 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -1019,7 +1011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1285,15 +1277,6 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1309,42 +1292,42 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1363,7 +1346,7 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1405,13 +1388,13 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1420,23 +1403,32 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="3" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -1444,8 +1436,11 @@
     <xf numFmtId="166" fontId="12" fillId="3" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="3" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -1453,25 +1448,13 @@
     <xf numFmtId="166" fontId="12" fillId="3" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1486,13 +1469,13 @@
     <xf numFmtId="166" fontId="12" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="12" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1504,26 +1487,32 @@
     <xf numFmtId="10" fontId="12" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="10" fontId="12" fillId="4" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="4" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="10" fontId="12" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1534,28 +1523,22 @@
     <xf numFmtId="10" fontId="1" fillId="3" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1889,7 +1872,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y91"/>
+  <dimension ref="A1:Y110"/>
   <sheetFormatPr defaultRowHeight="24.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="13.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="46.33203125" style="1" customWidth="1"/>
@@ -2021,18 +2004,15 @@
       </c>
       <c r="D5" s="20">
         <f>968+172</f>
-        <v>1140</v>
       </c>
       <c r="E5" s="20">
         <v>1105</v>
       </c>
       <c r="F5" s="20">
         <f>965+172</f>
-        <v>1137</v>
       </c>
       <c r="G5" s="21">
         <f>615+164</f>
-        <v>779</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
@@ -2067,7 +2047,6 @@
       </c>
       <c r="E6" s="28">
         <f>70+62+3</f>
-        <v>135</v>
       </c>
       <c r="F6" s="28">
         <v>248</v>
@@ -2099,26 +2078,21 @@
       </c>
       <c r="B7" s="33">
         <f>431+134</f>
-        <v>565</v>
       </c>
       <c r="C7" s="34">
         <v>512</v>
       </c>
       <c r="D7" s="34">
         <f>420+123</f>
-        <v>543</v>
       </c>
       <c r="E7" s="34">
         <f>429+2+132</f>
-        <v>563</v>
       </c>
       <c r="F7" s="34">
         <f>393+120</f>
-        <v>513</v>
       </c>
       <c r="G7" s="35">
         <f>387+125</f>
-        <v>512</v>
       </c>
       <c r="H7" s="34"/>
       <c r="I7" s="34"/>
@@ -2184,7 +2158,6 @@
       </c>
       <c r="B9" s="33">
         <f>602+55</f>
-        <v>657</v>
       </c>
       <c r="C9" s="34">
         <v>304</v>
@@ -2194,15 +2167,12 @@
       </c>
       <c r="E9" s="34">
         <f>198+24+59</f>
-        <v>281</v>
       </c>
       <c r="F9" s="34">
         <f>367+90</f>
-        <v>457</v>
       </c>
       <c r="G9" s="35">
         <f>156+51</f>
-        <v>207</v>
       </c>
       <c r="H9" s="34"/>
       <c r="I9" s="40"/>
@@ -2228,18 +2198,15 @@
       </c>
       <c r="B10" s="33">
         <f>11+11</f>
-        <v>22</v>
       </c>
       <c r="C10" s="34">
         <v>7</v>
       </c>
       <c r="D10" s="34">
         <f>9+5</f>
-        <v>14</v>
       </c>
       <c r="E10" s="34">
         <f>2-4</f>
-        <v>-2</v>
       </c>
       <c r="F10" s="34">
         <v>0</v>
@@ -2271,7 +2238,6 @@
       </c>
       <c r="B11" s="33">
         <f>1+14+6</f>
-        <v>21</v>
       </c>
       <c r="C11" s="34">
         <v>6</v>
@@ -2312,7 +2278,6 @@
       </c>
       <c r="B12" s="33">
         <f>16+4</f>
-        <v>20</v>
       </c>
       <c r="C12" s="34">
         <v>18</v>
@@ -2393,19 +2358,15 @@
       </c>
       <c r="B14" s="33">
         <f>1653+326+30</f>
-        <v>2009</v>
       </c>
       <c r="C14" s="34">
         <f>960+313+245+2+76</f>
-        <v>1596</v>
       </c>
       <c r="D14" s="34">
         <f>1620+47</f>
-        <v>1667</v>
       </c>
       <c r="E14" s="34">
         <f>1096+338+254+46</f>
-        <v>1734</v>
       </c>
       <c r="F14" s="34">
         <v>1294</v>
@@ -2437,27 +2398,21 @@
       </c>
       <c r="B15" s="33">
         <f>47+28+59+19</f>
-        <v>153</v>
       </c>
       <c r="C15" s="34">
         <f>28+21+36+15</f>
-        <v>100</v>
       </c>
       <c r="D15" s="34">
         <f>25+14+50+16</f>
-        <v>105</v>
       </c>
       <c r="E15" s="34">
         <f>36+27+21</f>
-        <v>84</v>
       </c>
       <c r="F15" s="34">
         <f>42+47+23</f>
-        <v>112</v>
       </c>
       <c r="G15" s="35">
         <f>40+39+22</f>
-        <v>101</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
@@ -2483,27 +2438,21 @@
       </c>
       <c r="B16" s="33">
         <f>36+21+8</f>
-        <v>65</v>
       </c>
       <c r="C16" s="34">
         <f>27+5+18+5</f>
-        <v>55</v>
       </c>
       <c r="D16" s="34">
         <f>24+21+7</f>
-        <v>52</v>
       </c>
       <c r="E16" s="34">
         <f>27+26+4</f>
-        <v>57</v>
       </c>
       <c r="F16" s="34">
         <f>39+11+1</f>
-        <v>51</v>
       </c>
       <c r="G16" s="35">
         <f>33+28</f>
-        <v>61</v>
       </c>
       <c r="H16" s="34"/>
       <c r="I16" s="34"/>
@@ -2529,15 +2478,12 @@
       </c>
       <c r="B17" s="33">
         <f>205+65</f>
-        <v>270</v>
       </c>
       <c r="C17" s="34">
         <f>66+41</f>
-        <v>107</v>
       </c>
       <c r="D17" s="34">
         <f>142+43</f>
-        <v>185</v>
       </c>
       <c r="E17" s="34">
         <v>350</v>
@@ -2547,7 +2493,6 @@
       </c>
       <c r="G17" s="35">
         <f>155+50+1</f>
-        <v>206</v>
       </c>
       <c r="H17" s="34"/>
       <c r="I17" s="34"/>
@@ -2576,7 +2521,6 @@
       </c>
       <c r="C18" s="34">
         <f>310+3</f>
-        <v>313</v>
       </c>
       <c r="D18" s="34">
         <v>16</v>
@@ -2589,7 +2533,6 @@
       </c>
       <c r="G18" s="35">
         <f>158+174</f>
-        <v>332</v>
       </c>
       <c r="H18" s="34"/>
       <c r="I18" s="34"/>
@@ -2618,19 +2561,15 @@
       </c>
       <c r="C19" s="34">
         <f>238+50</f>
-        <v>288</v>
       </c>
       <c r="D19" s="34">
         <f>280+68</f>
-        <v>348</v>
       </c>
       <c r="E19" s="34">
         <f>155+30</f>
-        <v>185</v>
       </c>
       <c r="F19" s="34">
         <f>234+57</f>
-        <v>291</v>
       </c>
       <c r="G19" s="35">
         <v>598</v>
@@ -2779,26 +2718,21 @@
       </c>
       <c r="B23" s="33">
         <f>337+12</f>
-        <v>349</v>
       </c>
       <c r="C23" s="34">
         <f>96+177+8</f>
-        <v>281</v>
       </c>
       <c r="D23" s="34">
         <v>421</v>
       </c>
       <c r="E23" s="34">
         <f>94+219+4</f>
-        <v>317</v>
       </c>
       <c r="F23" s="34">
         <f>293+422+5</f>
-        <v>720</v>
       </c>
       <c r="G23" s="35">
         <f>286+10</f>
-        <v>296</v>
       </c>
       <c r="H23" s="34"/>
       <c r="I23" s="34"/>
@@ -2824,11 +2758,9 @@
       </c>
       <c r="B24" s="33">
         <f>108+53+4</f>
-        <v>165</v>
       </c>
       <c r="C24" s="34">
         <f>88+44+4</f>
-        <v>136</v>
       </c>
       <c r="D24" s="34">
         <v>143</v>
@@ -2838,7 +2770,6 @@
       </c>
       <c r="F24" s="34">
         <f>57+34+1</f>
-        <v>92</v>
       </c>
       <c r="G24" s="35">
         <v>108</v>
@@ -2882,7 +2813,6 @@
       </c>
       <c r="G25" s="35">
         <f>135+7</f>
-        <v>142</v>
       </c>
       <c r="H25" s="34"/>
       <c r="I25" s="34"/>
@@ -3032,14 +2962,12 @@
       </c>
       <c r="C29" s="49">
         <f>14+11</f>
-        <v>25</v>
       </c>
       <c r="D29" s="49">
         <v>35</v>
       </c>
       <c r="E29" s="49">
         <f>24+33</f>
-        <v>57</v>
       </c>
       <c r="F29" s="49">
         <v>11</v>
@@ -3183,28 +3111,16 @@
       </c>
       <c r="Y32" s="3"/>
     </row>
-    <row r="33" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="48">
-        <v>579</v>
-      </c>
-      <c r="C33" s="49">
-        <v>119</v>
-      </c>
-      <c r="D33" s="49">
-        <v>368</v>
-      </c>
-      <c r="E33" s="49">
-        <v>387</v>
-      </c>
-      <c r="F33" s="49">
-        <v>1093</v>
-      </c>
-      <c r="G33" s="50">
-        <v>1637</v>
-      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="50"/>
       <c r="H33" s="49"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -3221,30 +3137,17 @@
       <c r="Q33" s="26">
         <f>N33/O33</f>
       </c>
-      <c r="Y33" s="3"/>
-    </row>
-    <row r="34" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="48">
-        <v>956</v>
-      </c>
-      <c r="C34" s="49">
-        <v>791</v>
-      </c>
-      <c r="D34" s="49">
-        <v>934</v>
-      </c>
-      <c r="E34" s="49">
-        <v>972</v>
-      </c>
-      <c r="F34" s="49">
-        <v>768</v>
-      </c>
-      <c r="G34" s="50">
-        <v>2420</v>
-      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="50"/>
       <c r="H34" s="49"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -3261,25 +3164,29 @@
       <c r="Q34" s="26">
         <f>N34/O34</f>
       </c>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="50"/>
+      <c r="B35" s="48">
+        <v>579</v>
+      </c>
+      <c r="C35" s="49">
+        <v>119</v>
+      </c>
+      <c r="D35" s="49">
+        <v>368</v>
+      </c>
+      <c r="E35" s="49">
+        <v>387</v>
+      </c>
+      <c r="F35" s="49">
+        <v>1093</v>
+      </c>
+      <c r="G35" s="50">
+        <v>1637</v>
+      </c>
       <c r="H35" s="49"/>
       <c r="I35" s="49"/>
       <c r="J35" s="49"/>
@@ -3306,34 +3213,33 @@
       <c r="Y35" s="3"/>
     </row>
     <row r="36" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="54">
-        <v>2</v>
-      </c>
-      <c r="C36" s="55">
-        <v>10</v>
-      </c>
-      <c r="D36" s="55">
-        <v>1</v>
-      </c>
-      <c r="E36" s="55">
-        <v>10</v>
-      </c>
-      <c r="F36" s="55">
-        <v>0</v>
-      </c>
-      <c r="G36" s="56">
-        <f>10+23</f>
-        <v>33</v>
-      </c>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="57"/>
+      <c r="B36" s="48">
+        <v>956</v>
+      </c>
+      <c r="C36" s="49">
+        <v>791</v>
+      </c>
+      <c r="D36" s="49">
+        <v>934</v>
+      </c>
+      <c r="E36" s="49">
+        <v>972</v>
+      </c>
+      <c r="F36" s="49">
+        <v>768</v>
+      </c>
+      <c r="G36" s="50">
+        <v>2420</v>
+      </c>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="51"/>
       <c r="N36" s="31">
         <f>SUM(B36:M36)</f>
       </c>
@@ -3354,55 +3260,29 @@
       <c r="Y36" s="3"/>
     </row>
     <row r="37" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="1">
-        <f>SUM(B5:B36)</f>
-      </c>
-      <c r="C37" s="1">
-        <f>SUM(C5:C36)</f>
-      </c>
-      <c r="D37" s="1">
-        <f>SUM(D5:D36)</f>
-      </c>
-      <c r="E37" s="1">
-        <f>SUM(E5:E36)</f>
-      </c>
-      <c r="F37" s="1">
-        <f>SUM(F5:F36)</f>
-      </c>
-      <c r="G37" s="1">
-        <f>SUM(G5:G36)</f>
-      </c>
-      <c r="H37" s="1">
-        <f>SUM(H5:H36)</f>
-      </c>
-      <c r="I37" s="1">
-        <f>SUM(I5:I36)</f>
-      </c>
-      <c r="J37" s="1">
-        <f>SUM(J5:J36)</f>
-      </c>
-      <c r="K37" s="1">
-        <f>SUM(K5:K36)</f>
-      </c>
-      <c r="L37" s="1">
-        <f>SUM(L5:L36)</f>
-      </c>
-      <c r="M37" s="1">
-        <f>SUM(M5:M36)</f>
-      </c>
-      <c r="N37" s="9">
-        <f>SUM(N5:N36)</f>
-      </c>
-      <c r="O37" s="58">
-        <f>SUM(O5:O36)</f>
-      </c>
-      <c r="P37" s="16">
-        <f>SUM(P5:P36)</f>
-      </c>
-      <c r="Q37" s="59">
+      <c r="B37" s="48"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="31">
+        <f>SUM(B37:M37)</f>
+      </c>
+      <c r="O37" s="46"/>
+      <c r="P37" s="25">
+        <f>N37-O37</f>
+      </c>
+      <c r="Q37" s="26">
         <f>N37/O37</f>
       </c>
       <c r="R37" s="3"/>
@@ -3415,217 +3295,231 @@
       <c r="Y37" s="3"/>
     </row>
     <row r="38" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
+      <c r="B38" s="54">
+        <v>2</v>
+      </c>
+      <c r="C38" s="55">
+        <v>10</v>
+      </c>
+      <c r="D38" s="55">
+        <v>1</v>
+      </c>
+      <c r="E38" s="55">
+        <v>10</v>
+      </c>
+      <c r="F38" s="55">
+        <v>0</v>
+      </c>
+      <c r="G38" s="56">
+        <f>10+23</f>
+      </c>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="31">
+        <f>SUM(B38:M38)</f>
+      </c>
+      <c r="O38" s="46"/>
+      <c r="P38" s="25">
+        <f>N38-O38</f>
+      </c>
+      <c r="Q38" s="26">
+        <f>N38/O38</f>
+      </c>
       <c r="R38" s="3"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="7"/>
-      <c r="Y38" s="8"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
     </row>
     <row r="39" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="K39" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="O39" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="P39" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q39" s="17" t="s">
-        <v>18</v>
+      <c r="B39" s="1">
+        <f>SUM(B5:B38)</f>
+      </c>
+      <c r="C39" s="1">
+        <f>SUM(C5:C38)</f>
+      </c>
+      <c r="D39" s="1">
+        <f>SUM(D5:D38)</f>
+      </c>
+      <c r="E39" s="1">
+        <f>SUM(E5:E38)</f>
+      </c>
+      <c r="F39" s="1">
+        <f>SUM(F5:F38)</f>
+      </c>
+      <c r="G39" s="1">
+        <f>SUM(G5:G38)</f>
+      </c>
+      <c r="H39" s="1">
+        <f>SUM(H5:H38)</f>
+      </c>
+      <c r="I39" s="1">
+        <f>SUM(I5:I38)</f>
+      </c>
+      <c r="J39" s="1">
+        <f>SUM(J5:J38)</f>
+      </c>
+      <c r="K39" s="1">
+        <f>SUM(K5:K38)</f>
+      </c>
+      <c r="L39" s="1">
+        <f>SUM(L5:L38)</f>
+      </c>
+      <c r="M39" s="1">
+        <f>SUM(M5:M38)</f>
+      </c>
+      <c r="N39" s="9">
+        <f>SUM(N5:N38)</f>
+      </c>
+      <c r="O39" s="58">
+        <f>SUM(O5:O38)</f>
+      </c>
+      <c r="P39" s="16">
+        <f>SUM(P5:P38)</f>
+      </c>
+      <c r="Q39" s="59">
+        <f>N39/O39</f>
       </c>
       <c r="R39" s="3"/>
-      <c r="S39" s="2"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="8"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
     </row>
     <row r="40" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A40" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="64">
-        <v>69122.2</v>
-      </c>
-      <c r="C40" s="65">
-        <v>50104.68</v>
-      </c>
-      <c r="D40" s="65">
-        <v>63469.74</v>
-      </c>
-      <c r="E40" s="65">
-        <v>58369.04</v>
-      </c>
-      <c r="F40" s="65">
-        <v>58907.29</v>
-      </c>
-      <c r="G40" s="66">
-        <v>47511.6</v>
-      </c>
-      <c r="H40" s="65"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="69"/>
-      <c r="N40" s="70">
-        <f>SUM(B40:M40)</f>
-      </c>
-      <c r="O40" s="33"/>
-      <c r="P40" s="71">
-        <f>N40-O40</f>
-      </c>
-      <c r="Q40" s="72">
-        <f>N40/O40</f>
-      </c>
+      <c r="A40" s="3"/>
+      <c r="B40" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
       <c r="X40" s="7"/>
       <c r="Y40" s="8"/>
     </row>
     <row r="41" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" s="38">
-        <v>6713.4</v>
-      </c>
-      <c r="C41" s="73">
-        <v>7520</v>
-      </c>
-      <c r="D41" s="73">
-        <v>7832</v>
-      </c>
-      <c r="E41" s="73">
-        <v>6234</v>
-      </c>
-      <c r="F41" s="73">
-        <v>11513</v>
-      </c>
-      <c r="G41" s="74">
-        <v>9964</v>
-      </c>
-      <c r="H41" s="73"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="77"/>
-      <c r="M41" s="78"/>
-      <c r="N41" s="70">
-        <f>SUM(B41:M41)</f>
-      </c>
-      <c r="O41" s="33"/>
-      <c r="P41" s="71">
-        <f>N41-O41</f>
-      </c>
-      <c r="Q41" s="72">
-        <f>N41/O41</f>
+      <c r="A41" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O41" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="P41" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q41" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="7"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="8"/>
     </row>
-    <row r="42" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B42" s="42">
-        <v>48835.75</v>
-      </c>
-      <c r="C42" s="40">
-        <v>45119.5</v>
-      </c>
-      <c r="D42" s="40">
-        <v>47784.5</v>
-      </c>
-      <c r="E42" s="40">
-        <v>47601.75</v>
-      </c>
-      <c r="F42" s="40">
-        <v>44940.25</v>
-      </c>
-      <c r="G42" s="79">
-        <v>44199.5</v>
-      </c>
-      <c r="H42" s="40"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="80"/>
-      <c r="L42" s="77"/>
-      <c r="M42" s="81"/>
+    <row r="42" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A42" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="64">
+        <v>69122.2</v>
+      </c>
+      <c r="C42" s="65">
+        <v>50104.68</v>
+      </c>
+      <c r="D42" s="65">
+        <v>63469.74</v>
+      </c>
+      <c r="E42" s="65">
+        <v>58369.04</v>
+      </c>
+      <c r="F42" s="65">
+        <v>58907.29</v>
+      </c>
+      <c r="G42" s="66">
+        <v>47511.6</v>
+      </c>
+      <c r="H42" s="65"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="68"/>
+      <c r="M42" s="69"/>
       <c r="N42" s="70">
         <f>SUM(B42:M42)</f>
       </c>
@@ -3636,35 +3530,43 @@
       <c r="Q42" s="72">
         <f>N42/O42</f>
       </c>
-    </row>
-    <row r="43" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="8"/>
+    </row>
+    <row r="43" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="42">
-        <v>1932.05</v>
-      </c>
-      <c r="C43" s="40">
-        <v>2583.34</v>
-      </c>
-      <c r="D43" s="40">
-        <v>3600</v>
-      </c>
-      <c r="E43" s="40">
-        <v>2795</v>
-      </c>
-      <c r="F43" s="40">
-        <v>2843.25</v>
-      </c>
-      <c r="G43" s="79">
-        <v>3375</v>
-      </c>
-      <c r="H43" s="40"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="80"/>
+        <v>20</v>
+      </c>
+      <c r="B43" s="38">
+        <v>6713.4</v>
+      </c>
+      <c r="C43" s="73">
+        <v>7520</v>
+      </c>
+      <c r="D43" s="73">
+        <v>7832</v>
+      </c>
+      <c r="E43" s="73">
+        <v>6234</v>
+      </c>
+      <c r="F43" s="73">
+        <v>11513</v>
+      </c>
+      <c r="G43" s="74">
+        <v>9964</v>
+      </c>
+      <c r="H43" s="73"/>
+      <c r="I43" s="75"/>
+      <c r="J43" s="73"/>
+      <c r="K43" s="76"/>
       <c r="L43" s="77"/>
-      <c r="M43" s="81"/>
+      <c r="M43" s="78"/>
       <c r="N43" s="70">
         <f>SUM(B43:M43)</f>
       </c>
@@ -3675,28 +3577,36 @@
       <c r="Q43" s="72">
         <f>N43/O43</f>
       </c>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="8"/>
     </row>
     <row r="44" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="33">
-        <v>71821</v>
-      </c>
-      <c r="C44" s="34">
-        <v>30142</v>
+      <c r="A44" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="42">
+        <v>48835.75</v>
+      </c>
+      <c r="C44" s="40">
+        <v>45119.5</v>
       </c>
       <c r="D44" s="40">
-        <v>25332</v>
+        <v>47784.5</v>
       </c>
       <c r="E44" s="40">
-        <v>27851</v>
+        <v>47601.75</v>
       </c>
       <c r="F44" s="40">
-        <v>44346</v>
+        <v>44940.25</v>
       </c>
       <c r="G44" s="79">
-        <v>20753</v>
+        <v>44199.5</v>
       </c>
       <c r="H44" s="40"/>
       <c r="I44" s="42"/>
@@ -3717,25 +3627,25 @@
     </row>
     <row r="45" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" s="37">
-        <v>1078</v>
-      </c>
-      <c r="C45" s="34">
-        <v>686</v>
+        <v>56</v>
+      </c>
+      <c r="B45" s="42">
+        <v>1932.05</v>
+      </c>
+      <c r="C45" s="40">
+        <v>2583.34</v>
       </c>
       <c r="D45" s="40">
-        <v>686</v>
+        <v>3600</v>
       </c>
       <c r="E45" s="40">
-        <v>-147</v>
+        <v>2795</v>
       </c>
       <c r="F45" s="40">
-        <v>0</v>
+        <v>2843.25</v>
       </c>
       <c r="G45" s="79">
-        <v>588</v>
+        <v>3375</v>
       </c>
       <c r="H45" s="40"/>
       <c r="I45" s="42"/>
@@ -3755,26 +3665,26 @@
       </c>
     </row>
     <row r="46" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B46" s="42">
-        <v>1470</v>
-      </c>
-      <c r="C46" s="40">
-        <v>420</v>
+      <c r="A46" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="33">
+        <v>71821</v>
+      </c>
+      <c r="C46" s="34">
+        <v>30142</v>
       </c>
       <c r="D46" s="40">
-        <v>875</v>
+        <v>25332</v>
       </c>
       <c r="E46" s="40">
-        <v>1260</v>
+        <v>27851</v>
       </c>
       <c r="F46" s="40">
-        <v>1155</v>
+        <v>44346</v>
       </c>
       <c r="G46" s="79">
-        <v>-70</v>
+        <v>20753</v>
       </c>
       <c r="H46" s="40"/>
       <c r="I46" s="42"/>
@@ -3795,25 +3705,25 @@
     </row>
     <row r="47" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" s="42">
-        <v>1200</v>
-      </c>
-      <c r="C47" s="40">
-        <v>1200</v>
+        <v>24</v>
+      </c>
+      <c r="B47" s="37">
+        <v>1078</v>
+      </c>
+      <c r="C47" s="34">
+        <v>686</v>
       </c>
       <c r="D47" s="40">
-        <v>320</v>
+        <v>686</v>
       </c>
       <c r="E47" s="40">
-        <v>440</v>
+        <v>-147</v>
       </c>
       <c r="F47" s="40">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="G47" s="79">
-        <v>800</v>
+        <v>588</v>
       </c>
       <c r="H47" s="40"/>
       <c r="I47" s="42"/>
@@ -3834,32 +3744,32 @@
     </row>
     <row r="48" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B48" s="42">
-        <v>1615</v>
+        <v>1470</v>
       </c>
       <c r="C48" s="40">
-        <v>898.05</v>
+        <v>420</v>
       </c>
       <c r="D48" s="40">
-        <v>917.2</v>
+        <v>875</v>
       </c>
       <c r="E48" s="40">
-        <v>2150</v>
-      </c>
-      <c r="F48" s="82">
-        <v>1590</v>
+        <v>1260</v>
+      </c>
+      <c r="F48" s="40">
+        <v>1155</v>
       </c>
       <c r="G48" s="79">
-        <v>2518.48</v>
+        <v>-70</v>
       </c>
       <c r="H48" s="40"/>
       <c r="I48" s="42"/>
-      <c r="J48" s="83"/>
+      <c r="J48" s="40"/>
       <c r="K48" s="80"/>
       <c r="L48" s="77"/>
-      <c r="M48" s="84"/>
+      <c r="M48" s="81"/>
       <c r="N48" s="70">
         <f>SUM(B48:M48)</f>
       </c>
@@ -3873,25 +3783,25 @@
     </row>
     <row r="49" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="41" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B49" s="42">
-        <v>51083.47</v>
+        <v>1200</v>
       </c>
       <c r="C49" s="40">
-        <v>38867.18</v>
+        <v>1200</v>
       </c>
       <c r="D49" s="40">
-        <v>40827.75</v>
+        <v>320</v>
       </c>
       <c r="E49" s="40">
-        <v>44922.89</v>
+        <v>440</v>
       </c>
       <c r="F49" s="40">
-        <v>31969.05</v>
+        <v>640</v>
       </c>
       <c r="G49" s="79">
-        <v>38484.95</v>
+        <v>800</v>
       </c>
       <c r="H49" s="40"/>
       <c r="I49" s="42"/>
@@ -3912,37 +3822,32 @@
     </row>
     <row r="50" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B50" s="42">
-        <f>2580.2+3055.2</f>
-        <v>5635.4</v>
+        <v>1615</v>
       </c>
       <c r="C50" s="40">
-        <f>1464+1859</f>
-        <v>3323</v>
+        <v>898.05</v>
       </c>
       <c r="D50" s="40">
-        <v>3892.2</v>
+        <v>917.2</v>
       </c>
       <c r="E50" s="40">
-        <f>1313.4+1398.8</f>
-        <v>2712.2</v>
-      </c>
-      <c r="F50" s="40">
-        <f>1240.2+2453.4</f>
-        <v>3693.6000000000004</v>
+        <v>2150</v>
+      </c>
+      <c r="F50" s="82">
+        <v>1590</v>
       </c>
       <c r="G50" s="79">
-        <f>1440.4+2022.8</f>
-        <v>3463.2</v>
+        <v>2518.48</v>
       </c>
       <c r="H50" s="40"/>
       <c r="I50" s="42"/>
-      <c r="J50" s="40"/>
+      <c r="J50" s="83"/>
       <c r="K50" s="80"/>
       <c r="L50" s="77"/>
-      <c r="M50" s="81"/>
+      <c r="M50" s="84"/>
       <c r="N50" s="70">
         <f>SUM(B50:M50)</f>
       </c>
@@ -3956,30 +3861,25 @@
     </row>
     <row r="51" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B51" s="42">
-        <f>4320+2835</f>
-        <v>7155</v>
+        <v>51083.47</v>
       </c>
       <c r="C51" s="40">
-        <f>3705.75+2342.25</f>
-        <v>6048</v>
+        <v>38867.18</v>
       </c>
       <c r="D51" s="40">
-        <v>5656.5</v>
+        <v>40827.75</v>
       </c>
       <c r="E51" s="40">
-        <f>2814.75+3510</f>
-        <v>6324.75</v>
+        <v>44922.89</v>
       </c>
       <c r="F51" s="40">
-        <f>4331.5+1208.25</f>
-        <v>5539.75</v>
+        <v>31969.05</v>
       </c>
       <c r="G51" s="79">
-        <f>3618+2970</f>
-        <v>6588</v>
+        <v>38484.95</v>
       </c>
       <c r="H51" s="40"/>
       <c r="I51" s="42"/>
@@ -3999,26 +3899,26 @@
       </c>
     </row>
     <row r="52" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="85" t="s">
-        <v>31</v>
+      <c r="A52" s="41" t="s">
+        <v>29</v>
       </c>
       <c r="B52" s="42">
-        <v>7759.2</v>
+        <f>2580.2+3055.2</f>
       </c>
       <c r="C52" s="40">
-        <v>5893.8</v>
+        <f>1464+1859</f>
       </c>
       <c r="D52" s="40">
-        <v>5343.3</v>
+        <v>3892.2</v>
       </c>
       <c r="E52" s="40">
-        <v>10020.6</v>
-      </c>
-      <c r="F52" s="82">
-        <v>5639.2</v>
+        <f>1313.4+1398.8</f>
+      </c>
+      <c r="F52" s="40">
+        <f>1240.2+2453.4</f>
       </c>
       <c r="G52" s="79">
-        <v>5905.2</v>
+        <f>1440.4+2022.8</f>
       </c>
       <c r="H52" s="40"/>
       <c r="I52" s="42"/>
@@ -4038,26 +3938,26 @@
       </c>
     </row>
     <row r="53" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
-        <v>32</v>
+      <c r="A53" s="41" t="s">
+        <v>30</v>
       </c>
       <c r="B53" s="42">
-        <v>342</v>
+        <f>4320+2835</f>
       </c>
       <c r="C53" s="40">
-        <v>3344.11</v>
+        <f>3705.75+2342.25</f>
       </c>
       <c r="D53" s="40">
-        <v>456</v>
+        <v>5656.5</v>
       </c>
       <c r="E53" s="40">
-        <v>188</v>
+        <f>2814.75+3510</f>
       </c>
       <c r="F53" s="40">
-        <v>266</v>
+        <f>4331.5+1208.25</f>
       </c>
       <c r="G53" s="79">
-        <v>1136.68</v>
+        <f>3618+2970</f>
       </c>
       <c r="H53" s="40"/>
       <c r="I53" s="42"/>
@@ -4077,26 +3977,26 @@
       </c>
     </row>
     <row r="54" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="45" t="s">
-        <v>33</v>
+      <c r="A54" s="85" t="s">
+        <v>31</v>
       </c>
       <c r="B54" s="42">
-        <v>13061</v>
+        <v>7759.2</v>
       </c>
       <c r="C54" s="40">
-        <v>8396.9</v>
+        <v>5893.8</v>
       </c>
       <c r="D54" s="40">
-        <v>11200</v>
+        <v>5343.3</v>
       </c>
       <c r="E54" s="40">
-        <v>6205</v>
-      </c>
-      <c r="F54" s="40">
-        <v>9440</v>
+        <v>10020.6</v>
+      </c>
+      <c r="F54" s="82">
+        <v>5639.2</v>
       </c>
       <c r="G54" s="79">
-        <v>22221.24</v>
+        <v>5905.2</v>
       </c>
       <c r="H54" s="40"/>
       <c r="I54" s="42"/>
@@ -4117,99 +4017,103 @@
     </row>
     <row r="55" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B55" s="42">
-        <v>175</v>
+        <v>342</v>
       </c>
       <c r="C55" s="40">
-        <v>297.5</v>
+        <v>3344.11</v>
       </c>
       <c r="D55" s="40">
-        <v>1540.8</v>
+        <v>456</v>
       </c>
       <c r="E55" s="40">
-        <v>507.5</v>
+        <v>188</v>
       </c>
       <c r="F55" s="40">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="G55" s="79">
-        <v>140</v>
+        <v>1136.68</v>
       </c>
       <c r="H55" s="40"/>
       <c r="I55" s="42"/>
       <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
+      <c r="K55" s="80"/>
       <c r="L55" s="77"/>
       <c r="M55" s="81"/>
       <c r="N55" s="70">
         <f>SUM(B55:M55)</f>
       </c>
-      <c r="O55" s="48"/>
-      <c r="P55" s="86">
+      <c r="O55" s="33"/>
+      <c r="P55" s="71">
         <f>N55-O55</f>
       </c>
-      <c r="Q55" s="87">
+      <c r="Q55" s="72">
         <f>N55/O55</f>
       </c>
     </row>
     <row r="56" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="45" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B56" s="42">
-        <v>19662.5</v>
+        <v>13061</v>
       </c>
       <c r="C56" s="40">
-        <v>24514.15</v>
+        <v>8396.9</v>
       </c>
       <c r="D56" s="40">
-        <v>20371.6</v>
+        <v>11200</v>
       </c>
       <c r="E56" s="40">
-        <v>19719.58</v>
+        <v>6205</v>
       </c>
       <c r="F56" s="40">
-        <v>16992.5</v>
+        <v>9440</v>
       </c>
       <c r="G56" s="79">
-        <v>14051.65</v>
+        <v>22221.24</v>
       </c>
       <c r="H56" s="40"/>
-      <c r="I56" s="88"/>
+      <c r="I56" s="42"/>
       <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
+      <c r="K56" s="80"/>
       <c r="L56" s="77"/>
       <c r="M56" s="81"/>
       <c r="N56" s="70">
         <f>SUM(B56:M56)</f>
       </c>
-      <c r="O56" s="89"/>
-      <c r="P56" s="90"/>
-      <c r="Q56" s="91"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="71">
+        <f>N56-O56</f>
+      </c>
+      <c r="Q56" s="72">
+        <f>N56/O56</f>
+      </c>
     </row>
     <row r="57" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B57" s="42">
-        <v>9265</v>
+        <v>175</v>
       </c>
       <c r="C57" s="40">
-        <v>3360</v>
+        <v>297.5</v>
       </c>
       <c r="D57" s="40">
-        <v>3601.6</v>
+        <v>1540.8</v>
       </c>
       <c r="E57" s="40">
-        <v>4556.29</v>
+        <v>507.5</v>
       </c>
       <c r="F57" s="40">
-        <v>4372.5</v>
+        <v>210</v>
       </c>
       <c r="G57" s="79">
-        <v>4790</v>
+        <v>140</v>
       </c>
       <c r="H57" s="40"/>
       <c r="I57" s="42"/>
@@ -4220,116 +4124,112 @@
       <c r="N57" s="70">
         <f>SUM(B57:M57)</f>
       </c>
-      <c r="O57" s="89"/>
-      <c r="P57" s="90"/>
-      <c r="Q57" s="91"/>
+      <c r="O57" s="48"/>
+      <c r="P57" s="86">
+        <f>N57-O57</f>
+      </c>
+      <c r="Q57" s="87">
+        <f>N57/O57</f>
+      </c>
     </row>
     <row r="58" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B58" s="42">
-        <v>7422.5</v>
+        <v>19662.5</v>
       </c>
       <c r="C58" s="40">
-        <v>6260</v>
+        <v>24514.15</v>
       </c>
       <c r="D58" s="40">
-        <v>9391.65</v>
+        <v>20371.6</v>
       </c>
       <c r="E58" s="40">
-        <v>7145</v>
+        <v>19719.58</v>
       </c>
       <c r="F58" s="40">
-        <v>14852.5</v>
+        <v>16992.5</v>
       </c>
       <c r="G58" s="79">
-        <v>6130.8</v>
+        <v>14051.65</v>
       </c>
       <c r="H58" s="40"/>
-      <c r="I58" s="42"/>
+      <c r="I58" s="88"/>
       <c r="J58" s="40"/>
-      <c r="K58" s="80"/>
+      <c r="K58" s="40"/>
       <c r="L58" s="77"/>
-      <c r="M58" s="92"/>
+      <c r="M58" s="81"/>
       <c r="N58" s="70">
         <f>SUM(B58:M58)</f>
       </c>
-      <c r="O58" s="27"/>
-      <c r="P58" s="71">
-        <f>N58-O58</f>
-      </c>
-      <c r="Q58" s="26">
-        <f>N58/O58</f>
-      </c>
+      <c r="O58" s="48"/>
+      <c r="P58" s="86"/>
+      <c r="Q58" s="87"/>
     </row>
     <row r="59" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="38">
-        <v>6356</v>
+      <c r="A59" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" s="42">
+        <v>9265</v>
       </c>
       <c r="C59" s="40">
-        <v>5196</v>
+        <v>3360</v>
       </c>
       <c r="D59" s="40">
-        <v>5715</v>
+        <v>3601.6</v>
       </c>
       <c r="E59" s="40">
-        <v>5778</v>
+        <v>4556.29</v>
       </c>
       <c r="F59" s="40">
-        <v>3434</v>
+        <v>4372.5</v>
       </c>
       <c r="G59" s="79">
-        <v>4242</v>
+        <v>4790</v>
       </c>
       <c r="H59" s="40"/>
       <c r="I59" s="42"/>
       <c r="J59" s="40"/>
-      <c r="K59" s="80"/>
+      <c r="K59" s="40"/>
       <c r="L59" s="77"/>
       <c r="M59" s="81"/>
       <c r="N59" s="70">
         <f>SUM(B59:M59)</f>
       </c>
-      <c r="O59" s="27"/>
-      <c r="P59" s="71">
-        <f>N59-O59</f>
-      </c>
-      <c r="Q59" s="72">
-        <f>N59/O59</f>
-      </c>
+      <c r="O59" s="48"/>
+      <c r="P59" s="86"/>
+      <c r="Q59" s="87"/>
     </row>
     <row r="60" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="85" t="s">
-        <v>39</v>
+      <c r="A60" s="45" t="s">
+        <v>37</v>
       </c>
       <c r="B60" s="42">
-        <v>6657.75</v>
+        <v>7422.5</v>
       </c>
       <c r="C60" s="40">
-        <v>4635</v>
+        <v>6260</v>
       </c>
       <c r="D60" s="40">
-        <v>7065</v>
+        <v>9391.65</v>
       </c>
       <c r="E60" s="40">
-        <v>5940</v>
+        <v>7145</v>
       </c>
       <c r="F60" s="40">
-        <v>3262.5</v>
+        <v>14852.5</v>
       </c>
       <c r="G60" s="79">
-        <v>5625</v>
+        <v>6130.8</v>
       </c>
       <c r="H60" s="40"/>
       <c r="I60" s="42"/>
       <c r="J60" s="40"/>
       <c r="K60" s="80"/>
       <c r="L60" s="77"/>
-      <c r="M60" s="81"/>
+      <c r="M60" s="89"/>
       <c r="N60" s="70">
         <f>SUM(B60:M60)</f>
       </c>
@@ -4337,36 +4237,31 @@
       <c r="P60" s="71">
         <f>N60-O60</f>
       </c>
-      <c r="Q60" s="72">
+      <c r="Q60" s="26">
         <f>N60/O60</f>
       </c>
     </row>
     <row r="61" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="42">
-        <f>750+220</f>
-        <v>970</v>
+      <c r="A61" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="38">
+        <v>6356</v>
       </c>
       <c r="C61" s="40">
-        <f>150+220</f>
-        <v>370</v>
+        <v>5196</v>
       </c>
       <c r="D61" s="40">
-        <f>750+220</f>
-        <v>970</v>
+        <v>5715</v>
       </c>
       <c r="E61" s="40">
-        <f>1800+440</f>
-        <v>2240</v>
+        <v>5778</v>
       </c>
       <c r="F61" s="40">
-        <v>2100</v>
+        <v>3434</v>
       </c>
       <c r="G61" s="79">
-        <f>1390+660</f>
-        <v>2050</v>
+        <v>4242</v>
       </c>
       <c r="H61" s="40"/>
       <c r="I61" s="42"/>
@@ -4377,7 +4272,7 @@
       <c r="N61" s="70">
         <f>SUM(B61:M61)</f>
       </c>
-      <c r="O61" s="33"/>
+      <c r="O61" s="27"/>
       <c r="P61" s="71">
         <f>N61-O61</f>
       </c>
@@ -4387,36 +4282,36 @@
     </row>
     <row r="62" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="85" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B62" s="42">
-        <v>2446</v>
+        <v>6657.75</v>
       </c>
       <c r="C62" s="40">
-        <v>2795.9</v>
+        <v>4635</v>
       </c>
       <c r="D62" s="40">
-        <v>1357.9</v>
+        <v>7065</v>
       </c>
       <c r="E62" s="40">
-        <v>3234.6</v>
-      </c>
-      <c r="F62" s="82">
-        <v>6372.1</v>
+        <v>5940</v>
+      </c>
+      <c r="F62" s="40">
+        <v>3262.5</v>
       </c>
       <c r="G62" s="79">
-        <v>3193</v>
+        <v>5625</v>
       </c>
       <c r="H62" s="40"/>
       <c r="I62" s="42"/>
       <c r="J62" s="40"/>
       <c r="K62" s="80"/>
-      <c r="L62" s="93"/>
+      <c r="L62" s="77"/>
       <c r="M62" s="81"/>
       <c r="N62" s="70">
         <f>SUM(B62:M62)</f>
       </c>
-      <c r="O62" s="33"/>
+      <c r="O62" s="27"/>
       <c r="P62" s="71">
         <f>N62-O62</f>
       </c>
@@ -4425,38 +4320,37 @@
       </c>
     </row>
     <row r="63" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="94">
-        <v>3065</v>
-      </c>
-      <c r="C63" s="94">
-        <v>380</v>
-      </c>
-      <c r="D63" s="94">
-        <v>2883</v>
-      </c>
-      <c r="E63" s="94">
-        <v>2904.55</v>
-      </c>
-      <c r="F63" s="94">
-        <f>1538+375</f>
-        <v>1913</v>
-      </c>
-      <c r="G63" s="95">
-        <v>4241</v>
-      </c>
-      <c r="H63" s="94"/>
-      <c r="I63" s="94"/>
-      <c r="J63" s="96"/>
-      <c r="K63" s="97"/>
+      <c r="A63" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="42">
+        <f>750+220</f>
+      </c>
+      <c r="C63" s="40">
+        <f>150+220</f>
+      </c>
+      <c r="D63" s="40">
+        <f>750+220</f>
+      </c>
+      <c r="E63" s="40">
+        <f>1800+440</f>
+      </c>
+      <c r="F63" s="40">
+        <v>2100</v>
+      </c>
+      <c r="G63" s="79">
+        <f>1390+660</f>
+      </c>
+      <c r="H63" s="40"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="80"/>
       <c r="L63" s="77"/>
-      <c r="M63" s="98"/>
+      <c r="M63" s="81"/>
       <c r="N63" s="70">
         <f>SUM(B63:M63)</f>
       </c>
-      <c r="O63" s="48"/>
+      <c r="O63" s="33"/>
       <c r="P63" s="71">
         <f>N63-O63</f>
       </c>
@@ -4466,36 +4360,36 @@
     </row>
     <row r="64" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="94">
-        <v>5040</v>
-      </c>
-      <c r="C64" s="94">
-        <v>2240</v>
-      </c>
-      <c r="D64" s="94">
-        <v>2800</v>
-      </c>
-      <c r="E64" s="94">
-        <v>3360</v>
-      </c>
-      <c r="F64" s="99">
-        <v>1120</v>
-      </c>
-      <c r="G64" s="100">
-        <v>0</v>
-      </c>
-      <c r="H64" s="94"/>
-      <c r="I64" s="94"/>
-      <c r="J64" s="96"/>
-      <c r="K64" s="97"/>
-      <c r="L64" s="93"/>
-      <c r="M64" s="98"/>
+        <v>41</v>
+      </c>
+      <c r="B64" s="42">
+        <v>2446</v>
+      </c>
+      <c r="C64" s="40">
+        <v>2795.9</v>
+      </c>
+      <c r="D64" s="40">
+        <v>1357.9</v>
+      </c>
+      <c r="E64" s="40">
+        <v>3234.6</v>
+      </c>
+      <c r="F64" s="82">
+        <v>6372.1</v>
+      </c>
+      <c r="G64" s="79">
+        <v>3193</v>
+      </c>
+      <c r="H64" s="40"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="80"/>
+      <c r="L64" s="90"/>
+      <c r="M64" s="81"/>
       <c r="N64" s="70">
         <f>SUM(B64:M64)</f>
       </c>
-      <c r="O64" s="48"/>
+      <c r="O64" s="33"/>
       <c r="P64" s="71">
         <f>N64-O64</f>
       </c>
@@ -4504,34 +4398,33 @@
       </c>
     </row>
     <row r="65" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65" s="85" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="94">
-        <v>10206</v>
-      </c>
-      <c r="C65" s="94">
-        <v>24008.4</v>
-      </c>
-      <c r="D65" s="94">
-        <v>11874</v>
-      </c>
-      <c r="E65" s="94">
-        <v>10466.4</v>
-      </c>
-      <c r="F65" s="94">
-        <v>6636</v>
-      </c>
-      <c r="G65" s="95">
-        <f>8018.4+1940.4+717.6+727.2</f>
-        <v>11403.6</v>
-      </c>
-      <c r="H65" s="94"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="96"/>
-      <c r="K65" s="97"/>
-      <c r="L65" s="93"/>
-      <c r="M65" s="98"/>
+      <c r="A65" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="91">
+        <v>3065</v>
+      </c>
+      <c r="C65" s="91">
+        <v>380</v>
+      </c>
+      <c r="D65" s="91">
+        <v>2883</v>
+      </c>
+      <c r="E65" s="91">
+        <v>2904.55</v>
+      </c>
+      <c r="F65" s="91">
+        <f>1538+375</f>
+      </c>
+      <c r="G65" s="92">
+        <v>4241</v>
+      </c>
+      <c r="H65" s="91"/>
+      <c r="I65" s="91"/>
+      <c r="J65" s="93"/>
+      <c r="K65" s="94"/>
+      <c r="L65" s="77"/>
+      <c r="M65" s="95"/>
       <c r="N65" s="70">
         <f>SUM(B65:M65)</f>
       </c>
@@ -4545,32 +4438,32 @@
     </row>
     <row r="66" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" s="94">
+        <v>44</v>
+      </c>
+      <c r="B66" s="91">
+        <v>5040</v>
+      </c>
+      <c r="C66" s="91">
+        <v>2240</v>
+      </c>
+      <c r="D66" s="91">
+        <v>2800</v>
+      </c>
+      <c r="E66" s="91">
+        <v>3360</v>
+      </c>
+      <c r="F66" s="96">
+        <v>1120</v>
+      </c>
+      <c r="G66" s="97">
         <v>0</v>
       </c>
-      <c r="C66" s="94">
-        <v>390</v>
-      </c>
-      <c r="D66" s="94">
-        <v>0</v>
-      </c>
-      <c r="E66" s="94">
-        <v>0</v>
-      </c>
-      <c r="F66" s="94">
-        <v>0</v>
-      </c>
-      <c r="G66" s="95">
-        <v>0</v>
-      </c>
-      <c r="H66" s="94"/>
-      <c r="I66" s="94"/>
-      <c r="J66" s="96"/>
-      <c r="K66" s="97"/>
-      <c r="L66" s="93"/>
-      <c r="M66" s="98"/>
+      <c r="H66" s="91"/>
+      <c r="I66" s="91"/>
+      <c r="J66" s="93"/>
+      <c r="K66" s="94"/>
+      <c r="L66" s="90"/>
+      <c r="M66" s="95"/>
       <c r="N66" s="70">
         <f>SUM(B66:M66)</f>
       </c>
@@ -4584,37 +4477,32 @@
     </row>
     <row r="67" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="94">
-        <f>3758+1482</f>
-        <v>5240</v>
-      </c>
-      <c r="C67" s="94">
-        <f>4256+2380</f>
+        <v>45</v>
+      </c>
+      <c r="B67" s="91">
+        <v>10206</v>
+      </c>
+      <c r="C67" s="91">
+        <v>24008.4</v>
+      </c>
+      <c r="D67" s="91">
+        <v>11874</v>
+      </c>
+      <c r="E67" s="91">
+        <v>10466.4</v>
+      </c>
+      <c r="F67" s="91">
         <v>6636</v>
       </c>
-      <c r="D67" s="94">
-        <f>7276+1120</f>
-        <v>8396</v>
-      </c>
-      <c r="E67" s="94">
-        <f>4160+7022</f>
-        <v>11182</v>
-      </c>
-      <c r="F67" s="94">
-        <v>3545</v>
-      </c>
-      <c r="G67" s="95">
-        <f>5114+3078</f>
-        <v>8192</v>
-      </c>
-      <c r="H67" s="94"/>
-      <c r="I67" s="94"/>
-      <c r="J67" s="96"/>
-      <c r="K67" s="97"/>
-      <c r="L67" s="77"/>
-      <c r="M67" s="98"/>
+      <c r="G67" s="92">
+        <f>8018.4+1940.4+717.6+727.2</f>
+      </c>
+      <c r="H67" s="91"/>
+      <c r="I67" s="91"/>
+      <c r="J67" s="93"/>
+      <c r="K67" s="94"/>
+      <c r="L67" s="90"/>
+      <c r="M67" s="95"/>
       <c r="N67" s="70">
         <f>SUM(B67:M67)</f>
       </c>
@@ -4628,490 +4516,400 @@
     </row>
     <row r="68" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="85" t="s">
-        <v>47</v>
-      </c>
-      <c r="B68" s="94">
-        <v>17371</v>
-      </c>
-      <c r="C68" s="94">
-        <v>3729</v>
-      </c>
-      <c r="D68" s="94">
-        <v>8568</v>
-      </c>
-      <c r="E68" s="94">
-        <v>7524</v>
-      </c>
-      <c r="F68" s="94">
-        <v>30367.2</v>
-      </c>
-      <c r="G68" s="101">
-        <v>36304</v>
-      </c>
-      <c r="H68" s="40"/>
-      <c r="I68" s="94"/>
-      <c r="J68" s="96"/>
-      <c r="K68" s="97"/>
-      <c r="L68" s="77"/>
-      <c r="M68" s="98"/>
+        <v>46</v>
+      </c>
+      <c r="B68" s="91">
+        <v>0</v>
+      </c>
+      <c r="C68" s="91">
+        <v>390</v>
+      </c>
+      <c r="D68" s="91">
+        <v>0</v>
+      </c>
+      <c r="E68" s="91">
+        <v>0</v>
+      </c>
+      <c r="F68" s="91">
+        <v>0</v>
+      </c>
+      <c r="G68" s="92">
+        <v>0</v>
+      </c>
+      <c r="H68" s="91"/>
+      <c r="I68" s="91"/>
+      <c r="J68" s="93"/>
+      <c r="K68" s="94"/>
+      <c r="L68" s="90"/>
+      <c r="M68" s="95"/>
       <c r="N68" s="70">
         <f>SUM(B68:M68)</f>
       </c>
       <c r="O68" s="48"/>
-      <c r="P68" s="86">
+      <c r="P68" s="71">
         <f>N68-O68</f>
       </c>
       <c r="Q68" s="72">
         <f>N68/O68</f>
       </c>
     </row>
-    <row r="69" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A69" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69" s="94">
-        <v>16731</v>
-      </c>
-      <c r="C69" s="94">
-        <v>14356.3</v>
-      </c>
-      <c r="D69" s="94">
-        <v>18706</v>
-      </c>
-      <c r="E69" s="94">
-        <v>17782.5</v>
-      </c>
-      <c r="F69" s="94">
-        <v>11215.5</v>
-      </c>
-      <c r="G69" s="101">
-        <v>61430</v>
-      </c>
-      <c r="H69" s="96"/>
-      <c r="I69" s="94"/>
-      <c r="J69" s="96"/>
-      <c r="K69" s="97"/>
-      <c r="L69" s="77"/>
-      <c r="M69" s="98"/>
+    <row r="69" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="85" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" s="91"/>
+      <c r="C69" s="91"/>
+      <c r="D69" s="91"/>
+      <c r="E69" s="91"/>
+      <c r="F69" s="91"/>
+      <c r="G69" s="92"/>
+      <c r="H69" s="91"/>
+      <c r="I69" s="91"/>
+      <c r="J69" s="93"/>
+      <c r="K69" s="94"/>
+      <c r="L69" s="90"/>
+      <c r="M69" s="95"/>
       <c r="N69" s="70">
         <f>SUM(B69:M69)</f>
       </c>
       <c r="O69" s="48"/>
-      <c r="P69" s="86">
+      <c r="P69" s="71">
         <f>N69-O69</f>
       </c>
       <c r="Q69" s="72">
         <f>N69/O69</f>
       </c>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="1"/>
-    </row>
-    <row r="70" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B70" s="94"/>
-      <c r="C70" s="94"/>
-      <c r="D70" s="94"/>
-      <c r="E70" s="94"/>
-      <c r="F70" s="94"/>
-      <c r="G70" s="101"/>
-      <c r="H70" s="96"/>
-      <c r="I70" s="94"/>
-      <c r="J70" s="96"/>
-      <c r="K70" s="97"/>
-      <c r="L70" s="77"/>
-      <c r="M70" s="98"/>
+    </row>
+    <row r="70" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="91"/>
+      <c r="C70" s="91"/>
+      <c r="D70" s="91"/>
+      <c r="E70" s="91"/>
+      <c r="F70" s="91"/>
+      <c r="G70" s="92"/>
+      <c r="H70" s="91"/>
+      <c r="I70" s="91"/>
+      <c r="J70" s="93"/>
+      <c r="K70" s="94"/>
+      <c r="L70" s="90"/>
+      <c r="M70" s="95"/>
       <c r="N70" s="70">
         <f>SUM(B70:M70)</f>
       </c>
       <c r="O70" s="48"/>
-      <c r="P70" s="86">
+      <c r="P70" s="71">
         <f>N70-O70</f>
       </c>
       <c r="Q70" s="72">
         <f>N70/O70</f>
       </c>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="1"/>
     </row>
     <row r="71" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71" s="53" t="s">
+      <c r="A71" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="91">
+        <f>3758+1482</f>
+      </c>
+      <c r="C71" s="91">
+        <f>4256+2380</f>
+      </c>
+      <c r="D71" s="91">
+        <f>7276+1120</f>
+      </c>
+      <c r="E71" s="91">
+        <f>4160+7022</f>
+      </c>
+      <c r="F71" s="91">
+        <v>3545</v>
+      </c>
+      <c r="G71" s="92">
+        <f>5114+3078</f>
+      </c>
+      <c r="H71" s="91"/>
+      <c r="I71" s="91"/>
+      <c r="J71" s="93"/>
+      <c r="K71" s="94"/>
+      <c r="L71" s="77"/>
+      <c r="M71" s="95"/>
+      <c r="N71" s="70">
+        <f>SUM(B71:M71)</f>
+      </c>
+      <c r="O71" s="48"/>
+      <c r="P71" s="71">
+        <f>N71-O71</f>
+      </c>
+      <c r="Q71" s="72">
+        <f>N71/O71</f>
+      </c>
+    </row>
+    <row r="72" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" s="91">
+        <v>17371</v>
+      </c>
+      <c r="C72" s="91">
+        <v>3729</v>
+      </c>
+      <c r="D72" s="91">
+        <v>8568</v>
+      </c>
+      <c r="E72" s="91">
+        <v>7524</v>
+      </c>
+      <c r="F72" s="91">
+        <v>30367.2</v>
+      </c>
+      <c r="G72" s="98">
+        <v>36304</v>
+      </c>
+      <c r="H72" s="40"/>
+      <c r="I72" s="91"/>
+      <c r="J72" s="93"/>
+      <c r="K72" s="94"/>
+      <c r="L72" s="77"/>
+      <c r="M72" s="95"/>
+      <c r="N72" s="70">
+        <f>SUM(B72:M72)</f>
+      </c>
+      <c r="O72" s="48"/>
+      <c r="P72" s="86">
+        <f>N72-O72</f>
+      </c>
+      <c r="Q72" s="72">
+        <f>N72/O72</f>
+      </c>
+    </row>
+    <row r="73" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A73" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B71" s="102">
-        <v>11150</v>
-      </c>
-      <c r="C71" s="103">
-        <v>120</v>
-      </c>
-      <c r="D71" s="103">
-        <v>35</v>
-      </c>
-      <c r="E71" s="103">
-        <v>120</v>
-      </c>
-      <c r="F71" s="104">
-        <v>0</v>
-      </c>
-      <c r="G71" s="105">
-        <f>120+430</f>
-        <v>550</v>
-      </c>
-      <c r="H71" s="103"/>
-      <c r="I71" s="102"/>
-      <c r="J71" s="103"/>
-      <c r="K71" s="106"/>
-      <c r="L71" s="107"/>
-      <c r="M71" s="108"/>
-      <c r="N71" s="53">
-        <f>SUM(B71:M71)</f>
-      </c>
-      <c r="O71" s="109"/>
-      <c r="P71" s="110">
-        <f>N71-O71</f>
-      </c>
-      <c r="Q71" s="111">
-        <f>N71/O71</f>
-      </c>
-    </row>
-    <row r="72" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B72" s="3">
-        <v>800</v>
-      </c>
-      <c r="C72" s="3">
-        <v>754.58</v>
-      </c>
-      <c r="D72" s="3">
-        <v>2350.9700000000003</v>
-      </c>
-      <c r="E72" s="112">
-        <v>4560.5</v>
-      </c>
-      <c r="F72" s="3">
-        <v>7137.07</v>
-      </c>
-      <c r="G72" s="3">
-        <f>1085.81-45.96</f>
-        <v>1039.85</v>
-      </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="112"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="52"/>
-      <c r="L72" s="77"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="1">
-        <f>SUM(B72:M72)</f>
-      </c>
-      <c r="O72" s="1"/>
-      <c r="P72" s="113"/>
-      <c r="Q72" s="114"/>
-    </row>
-    <row r="73" ht="24.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="115">
-        <f>SUM(B40:B72)</f>
-      </c>
-      <c r="C73" s="115">
-        <f>SUM(C40:C72)</f>
-      </c>
-      <c r="D73" s="115">
-        <f>SUM(D40:D72)</f>
-      </c>
-      <c r="E73" s="115">
-        <f>SUM(E40:E72)</f>
-      </c>
-      <c r="F73" s="115">
-        <f>SUM(F40:F72)</f>
-      </c>
-      <c r="G73" s="115">
-        <f>SUM(G40:G72)</f>
-      </c>
-      <c r="H73" s="115">
-        <f>SUM(H40:H72)</f>
-      </c>
-      <c r="I73" s="115">
-        <f>SUM(I40:I72)</f>
-      </c>
-      <c r="J73" s="115">
-        <f>SUM(J40:J72)</f>
-      </c>
-      <c r="K73" s="115">
-        <f>SUM(K40:K72)</f>
-      </c>
-      <c r="L73" s="115">
-        <f>SUM(L40:L72)</f>
-      </c>
-      <c r="M73" s="115">
-        <f>SUM(M40:M72)</f>
-      </c>
-      <c r="N73" s="115">
-        <f>SUM(N40:N72)</f>
-      </c>
-      <c r="O73" s="115">
-        <f>SUM(O40:O72)</f>
-      </c>
-      <c r="P73" s="115">
-        <f>SUM(P40:P72)</f>
-      </c>
-      <c r="Q73" s="116"/>
+      <c r="B73" s="91">
+        <v>16731</v>
+      </c>
+      <c r="C73" s="91">
+        <v>14356.3</v>
+      </c>
+      <c r="D73" s="91">
+        <v>18706</v>
+      </c>
+      <c r="E73" s="91">
+        <v>17782.5</v>
+      </c>
+      <c r="F73" s="91">
+        <v>11215.5</v>
+      </c>
+      <c r="G73" s="98">
+        <v>61430</v>
+      </c>
+      <c r="H73" s="93"/>
+      <c r="I73" s="91"/>
+      <c r="J73" s="93"/>
+      <c r="K73" s="94"/>
+      <c r="L73" s="77"/>
+      <c r="M73" s="95"/>
+      <c r="N73" s="70">
+        <f>SUM(B73:M73)</f>
+      </c>
+      <c r="O73" s="48"/>
+      <c r="P73" s="86">
+        <f>N73-O73</f>
+      </c>
+      <c r="Q73" s="72">
+        <f>N73/O73</f>
+      </c>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="1"/>
     </row>
     <row r="74" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="3"/>
-      <c r="B74" s="117"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="117"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="118"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="119"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="52"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
+      <c r="A74" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" s="91"/>
+      <c r="C74" s="91"/>
+      <c r="D74" s="91"/>
+      <c r="E74" s="91"/>
+      <c r="F74" s="91"/>
+      <c r="G74" s="98"/>
+      <c r="H74" s="93"/>
+      <c r="I74" s="91"/>
+      <c r="J74" s="93"/>
+      <c r="K74" s="94"/>
+      <c r="L74" s="77"/>
+      <c r="M74" s="95"/>
+      <c r="N74" s="70">
+        <f>SUM(B74:M74)</f>
+      </c>
+      <c r="O74" s="48"/>
+      <c r="P74" s="86">
+        <f>N74-O74</f>
+      </c>
+      <c r="Q74" s="72">
+        <f>N74/O74</f>
+      </c>
+      <c r="R74" s="3"/>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-    </row>
-    <row r="75" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A75" s="120" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H75" s="16" t="s">
+      <c r="Y74" s="1"/>
+    </row>
+    <row r="75" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75" s="99">
+        <v>11150</v>
+      </c>
+      <c r="C75" s="100">
+        <v>120</v>
+      </c>
+      <c r="D75" s="100">
+        <v>35</v>
+      </c>
+      <c r="E75" s="100">
+        <v>120</v>
+      </c>
+      <c r="F75" s="101">
+        <v>0</v>
+      </c>
+      <c r="G75" s="102">
+        <f>120+430</f>
+      </c>
+      <c r="H75" s="100"/>
+      <c r="I75" s="99"/>
+      <c r="J75" s="100"/>
+      <c r="K75" s="103"/>
+      <c r="L75" s="104"/>
+      <c r="M75" s="105"/>
+      <c r="N75" s="53">
+        <f>SUM(B75:M75)</f>
+      </c>
+      <c r="O75" s="106"/>
+      <c r="P75" s="107">
+        <f>N75-O75</f>
+      </c>
+      <c r="Q75" s="108">
+        <f>N75/O75</f>
+      </c>
+    </row>
+    <row r="76" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I75" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K75" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L75" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="M75" s="121" t="s">
-        <v>14</v>
-      </c>
-      <c r="N75" s="122" t="s">
-        <v>15</v>
-      </c>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="1"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-    </row>
-    <row r="76" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A76" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B76" s="123">
-        <v>347457</v>
-      </c>
-      <c r="C76" s="124">
-        <v>292601</v>
-      </c>
-      <c r="D76" s="124">
-        <v>332731</v>
-      </c>
-      <c r="E76" s="124">
-        <v>348211</v>
-      </c>
-      <c r="F76" s="124">
-        <v>312090</v>
-      </c>
-      <c r="G76" s="124">
-        <v>463303</v>
-      </c>
-      <c r="H76" s="124">
-        <v>339410</v>
-      </c>
-      <c r="I76" s="125">
-        <v>304583</v>
-      </c>
-      <c r="J76" s="125">
-        <v>369530</v>
-      </c>
-      <c r="K76" s="126">
-        <v>439368</v>
-      </c>
-      <c r="L76" s="125">
-        <v>465124</v>
-      </c>
-      <c r="M76" s="127">
-        <v>482659</v>
-      </c>
-      <c r="N76" s="128">
+      <c r="B76" s="3">
+        <v>800</v>
+      </c>
+      <c r="C76" s="3">
+        <v>754.58</v>
+      </c>
+      <c r="D76" s="3">
+        <v>2350.9700000000003</v>
+      </c>
+      <c r="E76" s="109">
+        <v>4560.5</v>
+      </c>
+      <c r="F76" s="3">
+        <v>7137.07</v>
+      </c>
+      <c r="G76" s="3">
+        <f>1085.81-45.96</f>
+      </c>
+      <c r="H76" s="3"/>
+      <c r="I76" s="109"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="52"/>
+      <c r="L76" s="77"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="1">
         <f>SUM(B76:M76)</f>
       </c>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="3"/>
-      <c r="T76" s="3"/>
-      <c r="U76" s="3"/>
-      <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-    </row>
-    <row r="77" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A77" s="129" t="s">
-        <v>61</v>
-      </c>
-      <c r="B77" s="130">
-        <f>B73</f>
-      </c>
-      <c r="C77" s="131">
-        <f>C73</f>
-      </c>
-      <c r="D77" s="131">
-        <f>D73</f>
-      </c>
-      <c r="E77" s="131">
-        <f>E73</f>
-      </c>
-      <c r="F77" s="131">
-        <f>F73</f>
-      </c>
-      <c r="G77" s="131">
-        <f>G73</f>
-      </c>
-      <c r="H77" s="131">
-        <f>H73</f>
-      </c>
-      <c r="I77" s="131">
-        <f>I73</f>
-      </c>
-      <c r="J77" s="131">
-        <f>J73</f>
-      </c>
-      <c r="K77" s="131">
-        <f>K73</f>
-      </c>
-      <c r="L77" s="131">
-        <f>L73</f>
-      </c>
-      <c r="M77" s="131">
-        <f>M73</f>
-      </c>
-      <c r="N77" s="131">
-        <f>N73</f>
-      </c>
-      <c r="O77" s="132"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="119"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="110"/>
+      <c r="Q76" s="111"/>
+    </row>
+    <row r="77" ht="24.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="112">
+        <f>SUM(B42:B76)</f>
+      </c>
+      <c r="C77" s="112">
+        <f>SUM(C42:C76)</f>
+      </c>
+      <c r="D77" s="112">
+        <f>SUM(D42:D76)</f>
+      </c>
+      <c r="E77" s="112">
+        <f>SUM(E42:E76)</f>
+      </c>
+      <c r="F77" s="112">
+        <f>SUM(F42:F76)</f>
+      </c>
+      <c r="G77" s="112">
+        <f>SUM(G42:G76)</f>
+      </c>
+      <c r="H77" s="112">
+        <f>SUM(H42:H76)</f>
+      </c>
+      <c r="I77" s="112">
+        <f>SUM(I42:I76)</f>
+      </c>
+      <c r="J77" s="112">
+        <f>SUM(J42:J76)</f>
+      </c>
+      <c r="K77" s="112">
+        <f>SUM(K42:K76)</f>
+      </c>
+      <c r="L77" s="112">
+        <f>SUM(L42:L76)</f>
+      </c>
+      <c r="M77" s="112">
+        <f>SUM(M42:M76)</f>
+      </c>
+      <c r="N77" s="112">
+        <f>SUM(N42:N76)</f>
+      </c>
+      <c r="O77" s="112">
+        <f>SUM(O42:O76)</f>
+      </c>
+      <c r="P77" s="112">
+        <f>SUM(P42:P76)</f>
+      </c>
+      <c r="Q77" s="113"/>
+      <c r="R77" s="3"/>
       <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
     </row>
     <row r="78" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A78" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78" s="24">
-        <f>B77-B76</f>
-      </c>
-      <c r="C78" s="24">
-        <f>C77-C76</f>
-      </c>
-      <c r="D78" s="24">
-        <f>D77-D76</f>
-      </c>
-      <c r="E78" s="24">
-        <f>E77-E76</f>
-      </c>
-      <c r="F78" s="24">
-        <f>F77-F76</f>
-      </c>
-      <c r="G78" s="24">
-        <f>G77-G76</f>
-      </c>
-      <c r="H78" s="24">
-        <f>H77-H76</f>
-      </c>
-      <c r="I78" s="24">
-        <f>I77-I76</f>
-      </c>
-      <c r="J78" s="24">
-        <f>J77-J76</f>
-      </c>
-      <c r="K78" s="24">
-        <f>K77-K76</f>
-      </c>
-      <c r="L78" s="24">
-        <f>L77-L76</f>
-      </c>
-      <c r="M78" s="24">
-        <f>M77-M76</f>
-      </c>
-      <c r="N78" s="24">
-        <f>SUM(B78:M78)</f>
-      </c>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-      <c r="Q78" s="3"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="114"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="114"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="115"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="116"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="52"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
@@ -5122,47 +4920,47 @@
       <c r="Y78" s="3"/>
     </row>
     <row r="79" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A79" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B79" s="133">
-        <f>B77/B76</f>
-      </c>
-      <c r="C79" s="134">
-        <f>C77/C76</f>
-      </c>
-      <c r="D79" s="134">
-        <f>D77/D76</f>
-      </c>
-      <c r="E79" s="134">
-        <f>E77/E76</f>
-      </c>
-      <c r="F79" s="134">
-        <f>F77/F76</f>
-      </c>
-      <c r="G79" s="134">
-        <f>G77/G76</f>
-      </c>
-      <c r="H79" s="134">
-        <f>H77/H76</f>
-      </c>
-      <c r="I79" s="134">
-        <f>I77/I76</f>
-      </c>
-      <c r="J79" s="134">
-        <f>J77/J76</f>
-      </c>
-      <c r="K79" s="134">
-        <f>K77/K76</f>
-      </c>
-      <c r="L79" s="134">
-        <f>L77/L76</f>
-      </c>
-      <c r="M79" s="134">
-        <f>M77/M76</f>
-      </c>
-      <c r="N79" s="134">
-        <f>N77/N76</f>
+      <c r="A79" s="117" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I79" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J79" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M79" s="118" t="s">
+        <v>14</v>
+      </c>
+      <c r="N79" s="119" t="s">
+        <v>15</v>
       </c>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
@@ -5177,20 +4975,48 @@
       <c r="Y79" s="3"/>
     </row>
     <row r="80" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="135"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="117"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-      <c r="N80" s="1"/>
+      <c r="A80" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="120">
+        <v>347457</v>
+      </c>
+      <c r="C80" s="121">
+        <v>292601</v>
+      </c>
+      <c r="D80" s="121">
+        <v>332731</v>
+      </c>
+      <c r="E80" s="121">
+        <v>348211</v>
+      </c>
+      <c r="F80" s="121">
+        <v>312090</v>
+      </c>
+      <c r="G80" s="121">
+        <v>463303</v>
+      </c>
+      <c r="H80" s="121">
+        <v>339410</v>
+      </c>
+      <c r="I80" s="122">
+        <v>304583</v>
+      </c>
+      <c r="J80" s="122">
+        <v>369530</v>
+      </c>
+      <c r="K80" s="123">
+        <v>439368</v>
+      </c>
+      <c r="L80" s="122">
+        <v>465124</v>
+      </c>
+      <c r="M80" s="124">
+        <v>482659</v>
+      </c>
+      <c r="N80" s="125">
+        <f>SUM(B80:M80)</f>
+      </c>
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
@@ -5204,24 +5030,52 @@
       <c r="Y80" s="3"/>
     </row>
     <row r="81" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="135"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="117"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
-      <c r="O81" s="3"/>
+      <c r="A81" s="126" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="127">
+        <f>B77</f>
+      </c>
+      <c r="C81" s="128">
+        <f>C77</f>
+      </c>
+      <c r="D81" s="128">
+        <f>D77</f>
+      </c>
+      <c r="E81" s="128">
+        <f>E77</f>
+      </c>
+      <c r="F81" s="128">
+        <f>F77</f>
+      </c>
+      <c r="G81" s="128">
+        <f>G77</f>
+      </c>
+      <c r="H81" s="128">
+        <f>H77</f>
+      </c>
+      <c r="I81" s="128">
+        <f>I77</f>
+      </c>
+      <c r="J81" s="128">
+        <f>J77</f>
+      </c>
+      <c r="K81" s="128">
+        <f>K77</f>
+      </c>
+      <c r="L81" s="128">
+        <f>L77</f>
+      </c>
+      <c r="M81" s="128">
+        <f>M77</f>
+      </c>
+      <c r="N81" s="128">
+        <f>N77</f>
+      </c>
+      <c r="O81" s="129"/>
       <c r="P81" s="3"/>
       <c r="Q81" s="3"/>
-      <c r="R81" s="1"/>
+      <c r="R81" s="116"/>
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
@@ -5231,20 +5085,48 @@
       <c r="Y81" s="3"/>
     </row>
     <row r="82" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="135"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="117"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
+      <c r="A82" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B82" s="24">
+        <f>B81-B80</f>
+      </c>
+      <c r="C82" s="24">
+        <f>C81-C80</f>
+      </c>
+      <c r="D82" s="24">
+        <f>D81-D80</f>
+      </c>
+      <c r="E82" s="24">
+        <f>E81-E80</f>
+      </c>
+      <c r="F82" s="24">
+        <f>F81-F80</f>
+      </c>
+      <c r="G82" s="24">
+        <f>G81-G80</f>
+      </c>
+      <c r="H82" s="24">
+        <f>H81-H80</f>
+      </c>
+      <c r="I82" s="24">
+        <f>I81-I80</f>
+      </c>
+      <c r="J82" s="24">
+        <f>J81-J80</f>
+      </c>
+      <c r="K82" s="24">
+        <f>K81-K80</f>
+      </c>
+      <c r="L82" s="24">
+        <f>L81-L80</f>
+      </c>
+      <c r="M82" s="24">
+        <f>M81-M80</f>
+      </c>
+      <c r="N82" s="24">
+        <f>SUM(B82:M82)</f>
+      </c>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
@@ -5258,47 +5140,47 @@
       <c r="Y82" s="3"/>
     </row>
     <row r="83" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A83" s="136" t="s">
-        <v>57</v>
-      </c>
-      <c r="B83" s="137" t="s">
-        <v>3</v>
-      </c>
-      <c r="C83" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I83" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J83" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K83" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L83" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="M83" s="138" t="s">
-        <v>14</v>
-      </c>
-      <c r="N83" s="120" t="s">
-        <v>15</v>
+      <c r="A83" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="130">
+        <f>B81/B80</f>
+      </c>
+      <c r="C83" s="131">
+        <f>C81/C80</f>
+      </c>
+      <c r="D83" s="131">
+        <f>D81/D80</f>
+      </c>
+      <c r="E83" s="131">
+        <f>E81/E80</f>
+      </c>
+      <c r="F83" s="131">
+        <f>F81/F80</f>
+      </c>
+      <c r="G83" s="131">
+        <f>G81/G80</f>
+      </c>
+      <c r="H83" s="131">
+        <f>H81/H80</f>
+      </c>
+      <c r="I83" s="131">
+        <f>I81/I80</f>
+      </c>
+      <c r="J83" s="131">
+        <f>J81/J80</f>
+      </c>
+      <c r="K83" s="131">
+        <f>K81/K80</f>
+      </c>
+      <c r="L83" s="131">
+        <f>L81/L80</f>
+      </c>
+      <c r="M83" s="131">
+        <f>M81/M80</f>
+      </c>
+      <c r="N83" s="131">
+        <f>N81/N80</f>
       </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
@@ -5313,48 +5195,20 @@
       <c r="Y83" s="3"/>
     </row>
     <row r="84" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A84" s="139" t="s">
-        <v>64</v>
-      </c>
-      <c r="B84" s="140">
-        <v>322860</v>
-      </c>
-      <c r="C84" s="141">
-        <v>268004</v>
-      </c>
-      <c r="D84" s="142">
-        <v>308134</v>
-      </c>
-      <c r="E84" s="142">
-        <v>321214</v>
-      </c>
-      <c r="F84" s="142">
-        <v>285093</v>
-      </c>
-      <c r="G84" s="142">
-        <v>436306</v>
-      </c>
-      <c r="H84" s="142">
-        <v>314813</v>
-      </c>
-      <c r="I84" s="142">
-        <v>279986</v>
-      </c>
-      <c r="J84" s="142">
-        <v>340133</v>
-      </c>
-      <c r="K84" s="142">
-        <v>409971</v>
-      </c>
-      <c r="L84" s="143">
-        <v>430927</v>
-      </c>
-      <c r="M84" s="144">
-        <v>448462</v>
-      </c>
-      <c r="N84" s="145">
-        <f>SUM(B84:M84)</f>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="132"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="114"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
@@ -5368,48 +5222,20 @@
       <c r="Y84" s="3"/>
     </row>
     <row r="85" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A85" s="146" t="s">
-        <v>65</v>
-      </c>
-      <c r="B85" s="147">
-        <v>347457</v>
-      </c>
-      <c r="C85" s="148">
-        <v>292601</v>
-      </c>
-      <c r="D85" s="149">
-        <v>332731</v>
-      </c>
-      <c r="E85" s="149">
-        <v>348211</v>
-      </c>
-      <c r="F85" s="149">
-        <v>312090</v>
-      </c>
-      <c r="G85" s="149">
-        <v>463303</v>
-      </c>
-      <c r="H85" s="149">
-        <v>339410</v>
-      </c>
-      <c r="I85" s="149">
-        <v>304583</v>
-      </c>
-      <c r="J85" s="149">
-        <v>369530</v>
-      </c>
-      <c r="K85" s="149">
-        <v>439368</v>
-      </c>
-      <c r="L85" s="149">
-        <v>465124</v>
-      </c>
-      <c r="M85" s="150">
-        <v>482659</v>
-      </c>
-      <c r="N85" s="151">
-        <f>SUM(B85:M85)</f>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="132"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="114"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
       <c r="Q85" s="3"/>
@@ -5423,48 +5249,20 @@
       <c r="Y85" s="3"/>
     </row>
     <row r="86" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A86" s="152" t="s">
-        <v>66</v>
-      </c>
-      <c r="B86" s="153">
-        <f>B85-B84</f>
-      </c>
-      <c r="C86" s="154">
-        <f>C85-C84</f>
-      </c>
-      <c r="D86" s="155">
-        <f>D85-D84</f>
-      </c>
-      <c r="E86" s="155">
-        <f>E85-E84</f>
-      </c>
-      <c r="F86" s="155">
-        <f>F85-F84</f>
-      </c>
-      <c r="G86" s="155">
-        <f>G85-G84</f>
-      </c>
-      <c r="H86" s="155">
-        <f>H85-H84</f>
-      </c>
-      <c r="I86" s="155">
-        <f>I85-I84</f>
-      </c>
-      <c r="J86" s="155">
-        <f>J85-J84</f>
-      </c>
-      <c r="K86" s="155">
-        <f>K85-K84</f>
-      </c>
-      <c r="L86" s="155">
-        <f>L85-L84</f>
-      </c>
-      <c r="M86" s="156">
-        <f>M85-M84</f>
-      </c>
-      <c r="N86" s="157">
-        <f>SUM(B86:M86)</f>
-      </c>
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="132"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="114"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
@@ -5478,47 +5276,47 @@
       <c r="Y86" s="3"/>
     </row>
     <row r="87" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A87" s="158" t="s">
-        <v>67</v>
-      </c>
-      <c r="B87" s="159">
-        <f>B86/B84</f>
-      </c>
-      <c r="C87" s="160">
-        <f>C86/C84</f>
-      </c>
-      <c r="D87" s="161">
-        <f>D86/D84</f>
-      </c>
-      <c r="E87" s="161">
-        <f>E86/E84</f>
-      </c>
-      <c r="F87" s="161">
-        <f>F86/F84</f>
-      </c>
-      <c r="G87" s="161">
-        <f>G86/G84</f>
-      </c>
-      <c r="H87" s="161">
-        <f>H86/H84</f>
-      </c>
-      <c r="I87" s="161">
-        <f>I86/I84</f>
-      </c>
-      <c r="J87" s="161">
-        <f>J86/J84</f>
-      </c>
-      <c r="K87" s="161">
-        <f>K86/K84</f>
-      </c>
-      <c r="L87" s="161">
-        <f>L86/L84</f>
-      </c>
-      <c r="M87" s="162">
-        <f>M86/M84</f>
-      </c>
-      <c r="N87" s="163">
-        <f>N86/N84</f>
+      <c r="A87" s="133" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" s="134" t="s">
+        <v>3</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H87" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I87" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J87" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K87" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L87" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M87" s="135" t="s">
+        <v>14</v>
+      </c>
+      <c r="N87" s="117" t="s">
+        <v>15</v>
       </c>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
@@ -5533,47 +5331,47 @@
       <c r="Y87" s="3"/>
     </row>
     <row r="88" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A88" s="164" t="s">
-        <v>61</v>
-      </c>
-      <c r="B88" s="164">
-        <f>B73</f>
-      </c>
-      <c r="C88" s="165">
-        <f>C73</f>
-      </c>
-      <c r="D88" s="165">
-        <f>D73</f>
-      </c>
-      <c r="E88" s="165">
-        <f>E73</f>
-      </c>
-      <c r="F88" s="165">
-        <f>F73</f>
-      </c>
-      <c r="G88" s="165">
-        <f>G73</f>
-      </c>
-      <c r="H88" s="165">
-        <f>H73</f>
-      </c>
-      <c r="I88" s="165">
-        <f>I73</f>
-      </c>
-      <c r="J88" s="165">
-        <f>J73</f>
-      </c>
-      <c r="K88" s="165">
-        <f>K73</f>
-      </c>
-      <c r="L88" s="165">
-        <f>L73</f>
-      </c>
-      <c r="M88" s="166">
-        <f>M73</f>
-      </c>
-      <c r="N88" s="167">
-        <f>N73</f>
+      <c r="A88" s="136" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" s="137">
+        <v>322860</v>
+      </c>
+      <c r="C88" s="138">
+        <v>268004</v>
+      </c>
+      <c r="D88" s="139">
+        <v>308134</v>
+      </c>
+      <c r="E88" s="139">
+        <v>321214</v>
+      </c>
+      <c r="F88" s="139">
+        <v>285093</v>
+      </c>
+      <c r="G88" s="139">
+        <v>436306</v>
+      </c>
+      <c r="H88" s="139">
+        <v>314813</v>
+      </c>
+      <c r="I88" s="139">
+        <v>279986</v>
+      </c>
+      <c r="J88" s="139">
+        <v>340133</v>
+      </c>
+      <c r="K88" s="139">
+        <v>409971</v>
+      </c>
+      <c r="L88" s="140">
+        <v>430927</v>
+      </c>
+      <c r="M88" s="141">
+        <v>448462</v>
+      </c>
+      <c r="N88" s="142">
+        <f>SUM(B88:M88)</f>
       </c>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
@@ -5588,47 +5386,47 @@
       <c r="Y88" s="3"/>
     </row>
     <row r="89" ht="24.75" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A89" s="168" t="s">
-        <v>68</v>
-      </c>
-      <c r="B89" s="169">
-        <f>B88/B84</f>
-      </c>
-      <c r="C89" s="170">
-        <f t="shared" ref="C89:N91" si="1">C88/C84</f>
-      </c>
-      <c r="D89" s="171">
-        <f>D88/D84</f>
-      </c>
-      <c r="E89" s="171">
-        <f>E88/E84</f>
-      </c>
-      <c r="F89" s="171">
-        <f>F88/F84</f>
-      </c>
-      <c r="G89" s="171">
-        <f>G88/G84</f>
-      </c>
-      <c r="H89" s="171">
-        <f>H88/H84</f>
-      </c>
-      <c r="I89" s="171">
-        <f>I88/I84</f>
-      </c>
-      <c r="J89" s="171">
-        <f>J88/J84</f>
-      </c>
-      <c r="K89" s="171">
-        <f>K88/K84</f>
-      </c>
-      <c r="L89" s="171">
-        <f>L88/L84</f>
-      </c>
-      <c r="M89" s="172">
-        <f>M88/M84</f>
-      </c>
-      <c r="N89" s="173">
-        <f>N88/N84</f>
+      <c r="A89" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" s="144">
+        <v>347457</v>
+      </c>
+      <c r="C89" s="145">
+        <v>292601</v>
+      </c>
+      <c r="D89" s="146">
+        <v>332731</v>
+      </c>
+      <c r="E89" s="146">
+        <v>348211</v>
+      </c>
+      <c r="F89" s="146">
+        <v>312090</v>
+      </c>
+      <c r="G89" s="146">
+        <v>463303</v>
+      </c>
+      <c r="H89" s="146">
+        <v>339410</v>
+      </c>
+      <c r="I89" s="146">
+        <v>304583</v>
+      </c>
+      <c r="J89" s="146">
+        <v>369530</v>
+      </c>
+      <c r="K89" s="146">
+        <v>439368</v>
+      </c>
+      <c r="L89" s="146">
+        <v>465124</v>
+      </c>
+      <c r="M89" s="147">
+        <v>482659</v>
+      </c>
+      <c r="N89" s="148">
+        <f>SUM(B89:M89)</f>
       </c>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
@@ -5642,107 +5440,582 @@
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
     </row>
-    <row r="90" ht="24.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="174" t="s">
+    <row r="90" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A90" s="149" t="s">
+        <v>68</v>
+      </c>
+      <c r="B90" s="150">
+        <f>B89-B88</f>
+      </c>
+      <c r="C90" s="151">
+        <f>C89-C88</f>
+      </c>
+      <c r="D90" s="152">
+        <f>D89-D88</f>
+      </c>
+      <c r="E90" s="152">
+        <f>E89-E88</f>
+      </c>
+      <c r="F90" s="152">
+        <f>F89-F88</f>
+      </c>
+      <c r="G90" s="152">
+        <f>G89-G88</f>
+      </c>
+      <c r="H90" s="152">
+        <f>H89-H88</f>
+      </c>
+      <c r="I90" s="152">
+        <f>I89-I88</f>
+      </c>
+      <c r="J90" s="152">
+        <f>J89-J88</f>
+      </c>
+      <c r="K90" s="152">
+        <f>K89-K88</f>
+      </c>
+      <c r="L90" s="152">
+        <f>L89-L88</f>
+      </c>
+      <c r="M90" s="153">
+        <f>M89-M88</f>
+      </c>
+      <c r="N90" s="154">
+        <f>SUM(B90:M90)</f>
+      </c>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A91" s="155" t="s">
         <v>69</v>
       </c>
-      <c r="B90" s="175">
-        <f>B88/B85</f>
-      </c>
-      <c r="C90" s="176">
-        <f>C88/C85</f>
-      </c>
-      <c r="D90" s="177">
-        <f>D88/D85</f>
-      </c>
-      <c r="E90" s="177">
-        <f>E88/E85</f>
-      </c>
-      <c r="F90" s="177">
-        <f>F88/F85</f>
-      </c>
-      <c r="G90" s="177">
-        <f>G88/G85</f>
-      </c>
-      <c r="H90" s="177">
-        <f>H88/H85</f>
-      </c>
-      <c r="I90" s="177">
-        <f>I88/I85</f>
-      </c>
-      <c r="J90" s="177">
-        <f>J88/J85</f>
-      </c>
-      <c r="K90" s="177">
-        <f>K88/K85</f>
-      </c>
-      <c r="L90" s="177">
-        <f>L88/L85</f>
-      </c>
-      <c r="M90" s="178">
-        <f>M88/M85</f>
-      </c>
-      <c r="N90" s="179">
-        <f>N88/N85</f>
-      </c>
-    </row>
-    <row r="91" ht="24.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="132">
-        <f>+B87-B88</f>
-        <v>0.09020098808315735</v>
-      </c>
-      <c r="C91" s="132">
-        <f t="shared" ref="C89:N89" si="0">+C87-C88</f>
-        <v>0.09553881059189728</v>
-      </c>
-      <c r="D91" s="132">
-        <f t="shared" si="1"/>
-        <v>0.07768750832297022</v>
-      </c>
-      <c r="E91" s="132">
-        <f t="shared" si="1"/>
-        <v>0.07819051231346985</v>
-      </c>
-      <c r="F91" s="132">
-        <f t="shared" si="1"/>
-        <v>0.10195398912613052</v>
-      </c>
-      <c r="G91" s="132">
-        <f t="shared" si="1"/>
-        <v>0.04952499129938359</v>
-      </c>
-      <c r="H91" s="132">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="I91" s="132">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="J91" s="132">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K91" s="132">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="L91" s="132">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="M91" s="132">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="N91" s="132">
-        <f t="shared" si="1"/>
-        <v>0.036601158835544656</v>
-      </c>
+      <c r="B91" s="156">
+        <f>B90/B88</f>
+      </c>
+      <c r="C91" s="157">
+        <f>C90/C88</f>
+      </c>
+      <c r="D91" s="158">
+        <f>D90/D88</f>
+      </c>
+      <c r="E91" s="158">
+        <f>E90/E88</f>
+      </c>
+      <c r="F91" s="158">
+        <f>F90/F88</f>
+      </c>
+      <c r="G91" s="158">
+        <f>G90/G88</f>
+      </c>
+      <c r="H91" s="158">
+        <f>H90/H88</f>
+      </c>
+      <c r="I91" s="158">
+        <f>I90/I88</f>
+      </c>
+      <c r="J91" s="158">
+        <f>J90/J88</f>
+      </c>
+      <c r="K91" s="158">
+        <f>K90/K88</f>
+      </c>
+      <c r="L91" s="158">
+        <f>L90/L88</f>
+      </c>
+      <c r="M91" s="159">
+        <f>M90/M88</f>
+      </c>
+      <c r="N91" s="160">
+        <f>N90/N88</f>
+      </c>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="1"/>
+      <c r="S91" s="3"/>
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+      <c r="X91" s="3"/>
+      <c r="Y91" s="3"/>
+    </row>
+    <row r="92" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A92" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="B92" s="161">
+        <f>B77</f>
+      </c>
+      <c r="C92" s="162">
+        <f>C77</f>
+      </c>
+      <c r="D92" s="162">
+        <f>D77</f>
+      </c>
+      <c r="E92" s="162">
+        <f>E77</f>
+      </c>
+      <c r="F92" s="162">
+        <f>F77</f>
+      </c>
+      <c r="G92" s="162">
+        <f>G77</f>
+      </c>
+      <c r="H92" s="162">
+        <f>H77</f>
+      </c>
+      <c r="I92" s="162">
+        <f>I77</f>
+      </c>
+      <c r="J92" s="162">
+        <f>J77</f>
+      </c>
+      <c r="K92" s="162">
+        <f>K77</f>
+      </c>
+      <c r="L92" s="162">
+        <f>L77</f>
+      </c>
+      <c r="M92" s="163">
+        <f>M77</f>
+      </c>
+      <c r="N92" s="164">
+        <f>N77</f>
+      </c>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+    </row>
+    <row r="93" ht="24.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A93" s="165" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93" s="166">
+        <f>B92/B88</f>
+      </c>
+      <c r="C93" s="167">
+        <f>C92/C88</f>
+      </c>
+      <c r="D93" s="168">
+        <f>D92/D88</f>
+      </c>
+      <c r="E93" s="168">
+        <f>E92/E88</f>
+      </c>
+      <c r="F93" s="168">
+        <f>F92/F88</f>
+      </c>
+      <c r="G93" s="168">
+        <f>G92/G88</f>
+      </c>
+      <c r="H93" s="168">
+        <f>H92/H88</f>
+      </c>
+      <c r="I93" s="168">
+        <f>I92/I88</f>
+      </c>
+      <c r="J93" s="168">
+        <f>J92/J88</f>
+      </c>
+      <c r="K93" s="168">
+        <f>K92/K88</f>
+      </c>
+      <c r="L93" s="168">
+        <f>L92/L88</f>
+      </c>
+      <c r="M93" s="169">
+        <f>M92/M88</f>
+      </c>
+      <c r="N93" s="170">
+        <f>N92/N88</f>
+      </c>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="3"/>
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
+      <c r="X93" s="3"/>
+      <c r="Y93" s="3"/>
+    </row>
+    <row r="94" ht="24.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="171" t="s">
+        <v>71</v>
+      </c>
+      <c r="B94" s="172">
+        <f>B92/B89</f>
+      </c>
+      <c r="C94" s="173">
+        <f>C92/C89</f>
+      </c>
+      <c r="D94" s="174">
+        <f>D92/D89</f>
+      </c>
+      <c r="E94" s="174">
+        <f>E92/E89</f>
+      </c>
+      <c r="F94" s="174">
+        <f>F92/F89</f>
+      </c>
+      <c r="G94" s="174">
+        <f>G92/G89</f>
+      </c>
+      <c r="H94" s="174">
+        <f>H92/H89</f>
+      </c>
+      <c r="I94" s="174">
+        <f>I92/I89</f>
+      </c>
+      <c r="J94" s="174">
+        <f>J92/J89</f>
+      </c>
+      <c r="K94" s="174">
+        <f>K92/K89</f>
+      </c>
+      <c r="L94" s="174">
+        <f>L92/L89</f>
+      </c>
+      <c r="M94" s="175">
+        <f>M92/M89</f>
+      </c>
+      <c r="N94" s="176">
+        <f>N92/N89</f>
+      </c>
+    </row>
+    <row r="95" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="B95" s="129"/>
+      <c r="C95" s="129"/>
+      <c r="D95" s="129"/>
+      <c r="E95" s="129"/>
+      <c r="F95" s="129"/>
+      <c r="G95" s="129"/>
+      <c r="H95" s="129"/>
+      <c r="I95" s="129"/>
+      <c r="J95" s="129"/>
+      <c r="K95" s="129"/>
+      <c r="L95" s="129"/>
+      <c r="M95" s="129"/>
+      <c r="N95" s="129"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="3"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="O105" s="3"/>
+      <c r="P105" s="3"/>
+      <c r="Q105" s="3"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="3"/>
+      <c r="Q107" s="3"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="O108" s="3"/>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1"/>
+      <c r="O110" s="3"/>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="O55:O57"/>
-    <mergeCell ref="P55:P57"/>
-    <mergeCell ref="Q55:Q57"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="O57:O59"/>
+    <mergeCell ref="P57:P59"/>
+    <mergeCell ref="Q57:Q59"/>
   </mergeCells>
   <conditionalFormatting sqref="Q5:Q8 Q11:Q37">
     <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
